--- a/resource/groundTruths/decision/CF_M06_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M06_ground_truth_decision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D682A3-04A6-EE41-A087-B1C283EE7568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD61753D-428C-824A-BE19-94DCCC9C4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16560" xr2:uid="{8FC4593B-E953-5C4A-A6FE-89BA102BF016}"/>
   </bookViews>
@@ -100,19 +100,19 @@
     <t>It is based on the React library, offering possibilities to incorporate native code for each platform. Due to the previous experience we already had with React, it seemed like a good idea to develop the project with this framework.</t>
   </si>
   <si>
-    <t>CF_M06_C06, CF_M06_C07</t>
-  </si>
-  <si>
-    <t>CF_M06_C06</t>
-  </si>
-  <si>
-    <t>CF_M06_C08</t>
-  </si>
-  <si>
-    <t>CF_M06_C02, CF_M06_C07, CF_M06_C08</t>
-  </si>
-  <si>
-    <t>CF_M06_C09</t>
+    <t>*CF_M06_C06, *CF_M06_C07</t>
+  </si>
+  <si>
+    <t>*CF_M06_C06</t>
+  </si>
+  <si>
+    <t>*CF_M06_C08</t>
+  </si>
+  <si>
+    <t>CF_M06_C02, *CF_M06_C07, *CF_M06_C08</t>
+  </si>
+  <si>
+    <t>*CF_M06_C09</t>
   </si>
 </sst>
 </file>

--- a/resource/groundTruths/decision/CF_M06_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M06_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD61753D-428C-824A-BE19-94DCCC9C4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73897EF4-2A6B-0643-A2B6-230606910EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16560" xr2:uid="{8FC4593B-E953-5C4A-A6FE-89BA102BF016}"/>
+    <workbookView xWindow="1800" yWindow="980" windowWidth="14480" windowHeight="16560" xr2:uid="{8FC4593B-E953-5C4A-A6FE-89BA102BF016}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>Document ID</t>
   </si>
@@ -43,9 +43,6 @@
     <t>AD ID</t>
   </si>
   <si>
-    <t>Architectural Element</t>
-  </si>
-  <si>
     <t>AD Source</t>
   </si>
   <si>
@@ -58,21 +55,6 @@
     <t>CF_M06</t>
   </si>
   <si>
-    <t>CF_M06_AD1</t>
-  </si>
-  <si>
-    <t>CF_M06_AD2</t>
-  </si>
-  <si>
-    <t>CF_M06_AD3</t>
-  </si>
-  <si>
-    <t>CF_M06_AD4</t>
-  </si>
-  <si>
-    <t>CF_M06_AD5</t>
-  </si>
-  <si>
     <t>Flux proposes an architecture in which the data flow is unidirectional, thus obtaining easier debugging and scalability.</t>
   </si>
   <si>
@@ -113,13 +95,58 @@
   </si>
   <si>
     <t>*CF_M06_C09</t>
+  </si>
+  <si>
+    <t>Architectural Element ID</t>
+  </si>
+  <si>
+    <t>CF_M06_AD01</t>
+  </si>
+  <si>
+    <t>CF_M06_AD02</t>
+  </si>
+  <si>
+    <t>CF_M06_AD03</t>
+  </si>
+  <si>
+    <t>CF_M06_AD04</t>
+  </si>
+  <si>
+    <t>CF_M06_AD05</t>
+  </si>
+  <si>
+    <t>Additionally, Redux offers a more familiar API for React developers, making it easier to integrate.</t>
+  </si>
+  <si>
+    <t>CF_M06_AD06</t>
+  </si>
+  <si>
+    <t>CF_M06_AD07</t>
+  </si>
+  <si>
+    <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API.</t>
+  </si>
+  <si>
+    <t>In addition, AWS SNS is more scalable and can be used by other services.</t>
+  </si>
+  <si>
+    <t>*CF_M06_C10</t>
+  </si>
+  <si>
+    <t>*CF_M06_C07</t>
+  </si>
+  <si>
+    <t>CF_M06_AU22</t>
+  </si>
+  <si>
+    <t>CF_M06_AD08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,6 +167,12 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -169,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -184,6 +217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1510777C-6F52-5F4C-A08E-7E22DAAD039A}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -509,33 +543,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
       </c>
       <c r="F2">
         <v>46</v>
@@ -543,19 +577,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
       </c>
       <c r="F3">
         <v>47</v>
@@ -563,19 +597,19 @@
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>49</v>
@@ -583,19 +617,19 @@
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>52</v>
@@ -603,22 +637,82 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
